--- a/Src/Assets/Common/Tables/Tables/ActionDefine.xlsx
+++ b/Src/Assets/Common/Tables/Tables/ActionDefine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0670AD99-1748-4B80-8C09-C82CA41AD7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576589CE-977A-44E0-A702-DA6C231890B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="599" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -439,6 +439,10 @@
     <t>激光炮</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
+  <si>
+    <t>isBasic</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -447,7 +451,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -582,8 +586,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -614,8 +624,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -633,6 +655,19 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -670,7 +705,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -713,6 +748,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="60% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -729,7 +773,64 @@
     <cellStyle name="好 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="适中 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="40">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1297,75 +1398,79 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A1:J5" totalsRowShown="0">
-  <autoFilter ref="A1:J5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Key" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Description" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{D2B0378F-2AC7-48BB-B226-76242E6C2C82}" name="Costs" dataDxfId="32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A1:K5" totalsRowShown="0">
+  <autoFilter ref="A1:K5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Key" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="37"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Description" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{D2B0378F-2AC7-48BB-B226-76242E6C2C82}" name="Costs" dataDxfId="35"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="TargetType"/>
-    <tableColumn id="4" xr3:uid="{D39F3B12-7181-4342-830A-9DA34F8EF285}" name="CD" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{B346CB5C-591C-4832-AA88-E75EBEBACD7E}" name="SupplyNumber" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{19483CEF-26D9-45EB-902B-73AF0CD7D822}" name="Target" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{C1E521C5-2F45-4AF1-A7CA-5C0C319A0BA4}" name="isCopy" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{D39F3B12-7181-4342-830A-9DA34F8EF285}" name="CD" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{B346CB5C-591C-4832-AA88-E75EBEBACD7E}" name="SupplyNumber" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{19483CEF-26D9-45EB-902B-73AF0CD7D822}" name="Target" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{C1E521C5-2F45-4AF1-A7CA-5C0C319A0BA4}" name="isCopy" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{9FDE5295-D11E-43B2-A44D-C11A54483AC1}" name="isBasic" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}" name="表1_3" displayName="表1_3" ref="A1:K14" totalsRowShown="0">
-  <autoFilter ref="A1:K14" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F3120D7C-A45E-4FA2-B5BE-40DA2E6B527D}" name="Key" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{DACBB893-CA05-4D02-85D5-4BD88763CDC8}" name="ID" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{E05E1824-9A14-47F2-A1F4-06305E7C3F01}" name="Name" dataDxfId="25"/>
-    <tableColumn id="24" xr3:uid="{05C56AEC-8EEB-4DC5-90D4-589693695F9F}" name="Description" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{ECB0F01F-2D12-43FF-88D0-8932B311B9C3}" name="Costs" dataDxfId="23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}" name="表1_3" displayName="表1_3" ref="A1:L14" totalsRowShown="0">
+  <autoFilter ref="A1:L14" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{F3120D7C-A45E-4FA2-B5BE-40DA2E6B527D}" name="Key" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{DACBB893-CA05-4D02-85D5-4BD88763CDC8}" name="ID" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{E05E1824-9A14-47F2-A1F4-06305E7C3F01}" name="Name" dataDxfId="28"/>
+    <tableColumn id="24" xr3:uid="{05C56AEC-8EEB-4DC5-90D4-589693695F9F}" name="Description" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{ECB0F01F-2D12-43FF-88D0-8932B311B9C3}" name="Costs" dataDxfId="26"/>
     <tableColumn id="11" xr3:uid="{8738C2BC-B1DC-4B88-A546-C9264D49325B}" name="TargetType"/>
-    <tableColumn id="6" xr3:uid="{A4A2D2D8-BA27-47D8-82A1-4708B0912A01}" name="CD" dataDxfId="22"/>
-    <tableColumn id="27" xr3:uid="{C523F30B-8528-475C-AB56-584489F12893}" name="Level" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{9F4863C8-14DF-490F-AAED-DA9CA6CCA3A6}" name="Damage" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{A4A2D2D8-BA27-47D8-82A1-4708B0912A01}" name="CD" dataDxfId="25"/>
+    <tableColumn id="27" xr3:uid="{C523F30B-8528-475C-AB56-584489F12893}" name="Level" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{9F4863C8-14DF-490F-AAED-DA9CA6CCA3A6}" name="Damage" dataDxfId="23"/>
     <tableColumn id="7" xr3:uid="{BB9F36B2-6C79-4196-AF6D-E44CF2743583}" name="Target"/>
     <tableColumn id="8" xr3:uid="{900D3857-3743-4154-8A5A-A6F00B9A5F63}" name="isCopy"/>
+    <tableColumn id="9" xr3:uid="{02DAE644-A845-4C22-A687-D868D5A5B60F}" name="isBasic"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BBDA416B-0922-4AAF-A799-D524740B3D14}" name="表1_4" displayName="表1_4" ref="A1:I5" totalsRowShown="0">
-  <autoFilter ref="A1:I5" xr:uid="{BBDA416B-0922-4AAF-A799-D524740B3D14}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{BE94463F-5F58-4AE5-8D3C-9ED629948C9E}" name="Key" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{65052D3C-90DB-42DF-8C3A-74AA612BEF48}" name="ID" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{2510B181-E22D-4568-AC36-382E43DA1F65}" name="Name" dataDxfId="17"/>
-    <tableColumn id="24" xr3:uid="{4BE18853-2496-4AA4-942D-324B9DDFB7C9}" name="Description" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{002F1A29-9EEC-44DB-A228-41BEF0AE2B11}" name="Costs" dataDxfId="15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BBDA416B-0922-4AAF-A799-D524740B3D14}" name="表1_4" displayName="表1_4" ref="A1:J5" totalsRowShown="0">
+  <autoFilter ref="A1:J5" xr:uid="{BBDA416B-0922-4AAF-A799-D524740B3D14}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{BE94463F-5F58-4AE5-8D3C-9ED629948C9E}" name="Key" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{65052D3C-90DB-42DF-8C3A-74AA612BEF48}" name="ID" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{2510B181-E22D-4568-AC36-382E43DA1F65}" name="Name" dataDxfId="20"/>
+    <tableColumn id="24" xr3:uid="{4BE18853-2496-4AA4-942D-324B9DDFB7C9}" name="Description" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{002F1A29-9EEC-44DB-A228-41BEF0AE2B11}" name="Costs" dataDxfId="18"/>
     <tableColumn id="11" xr3:uid="{45609FCE-4413-4353-9C89-BD89EFDE4C5D}" name="TargetType"/>
     <tableColumn id="4" xr3:uid="{3D0100FB-1F43-427C-8534-CDC24303D7E6}" name="CD"/>
-    <tableColumn id="6" xr3:uid="{734D322F-5955-4217-B185-B14B145BEC2D}" name="Target" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{D2799729-A837-4530-BC5D-075F4F0C2481}" name="isCopy" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{734D322F-5955-4217-B185-B14B145BEC2D}" name="Target" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{D2799729-A837-4530-BC5D-075F4F0C2481}" name="isCopy" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{2A54B557-3CDD-4506-B6E3-5A3D296C44C8}" name="isBasic" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8B3284A1-AA19-4A39-984C-72F0ECC55A5D}" name="表1_45" displayName="表1_45" ref="A1:I5" totalsRowShown="0">
-  <autoFilter ref="A1:I5" xr:uid="{8B3284A1-AA19-4A39-984C-72F0ECC55A5D}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{A1AF415F-7938-4DF8-BACD-2F3931097179}" name="Key" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{0F312E1F-9C3E-4D2C-9F68-C6E87C1EE718}" name="ID" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{B5C76171-0265-42F6-8D5B-4662AAE7F83A}" name="Name" dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{25AD89C3-2F76-4593-98BE-A3775460F142}" name="Description" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00DA4CE3-ED05-49B6-9190-58A0333EB78C}" name="Costs" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8B3284A1-AA19-4A39-984C-72F0ECC55A5D}" name="表1_45" displayName="表1_45" ref="A1:J5" totalsRowShown="0">
+  <autoFilter ref="A1:J5" xr:uid="{8B3284A1-AA19-4A39-984C-72F0ECC55A5D}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{A1AF415F-7938-4DF8-BACD-2F3931097179}" name="Key" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{0F312E1F-9C3E-4D2C-9F68-C6E87C1EE718}" name="ID" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{B5C76171-0265-42F6-8D5B-4662AAE7F83A}" name="Name" dataDxfId="13"/>
+    <tableColumn id="24" xr3:uid="{25AD89C3-2F76-4593-98BE-A3775460F142}" name="Description" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00DA4CE3-ED05-49B6-9190-58A0333EB78C}" name="Costs" dataDxfId="11"/>
     <tableColumn id="11" xr3:uid="{E2FEB15A-3782-40F3-A1CA-89D1DDC325AD}" name="TargetType"/>
     <tableColumn id="4" xr3:uid="{688FFF09-C71B-441C-B52A-14B5A669665E}" name="CD"/>
     <tableColumn id="6" xr3:uid="{98986103-0D74-481E-9EA2-26D93ECAF330}" name="Target"/>
     <tableColumn id="7" xr3:uid="{E9536439-71EB-48E6-A500-A711FD55C3A4}" name="isCopy"/>
+    <tableColumn id="8" xr3:uid="{A6F03304-4F13-4C9E-AD7B-C635338D9070}" name="isBasic" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1375,16 +1480,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CE1C72CE-D78A-4387-BD89-90EB97964EC3}" name="表1_6" displayName="表1_6" ref="A1:J3" totalsRowShown="0">
   <autoFilter ref="A1:J3" xr:uid="{CE1C72CE-D78A-4387-BD89-90EB97964EC3}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{18D4AA6C-FD21-4782-A770-E2A7E552A9B6}" name="Key" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{851BEEEC-EFAC-48C5-98CB-946D8978B5CF}" name="ID" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{9BAC052E-D5DE-43D9-917B-63EC0ABA7487}" name="Name" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{1FC82ABF-F7E7-4151-BE48-531952D84F64}" name="Description" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{18D4AA6C-FD21-4782-A770-E2A7E552A9B6}" name="Key" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{851BEEEC-EFAC-48C5-98CB-946D8978B5CF}" name="ID" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{9BAC052E-D5DE-43D9-917B-63EC0ABA7487}" name="Name" dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{1FC82ABF-F7E7-4151-BE48-531952D84F64}" name="Description" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{8B51D4EE-CB38-4B13-AF2A-6B841C4BBE98}" name="Costs"/>
     <tableColumn id="11" xr3:uid="{5A33598E-528B-42B6-9450-35112F1912EB}" name="TargetType"/>
-    <tableColumn id="25" xr3:uid="{F4682446-58E1-4CA5-A48B-3BFAAE53764B}" name="ItemType" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{0088744F-16F9-49C6-BB37-951ECCA67027}" name="CD" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{C97EB513-D794-47F8-B80D-94506BD82E97}" name="Target" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{47C97BCD-31D5-47E8-A5C1-ECCF343A6E95}" name="isCopy" dataDxfId="0"/>
+    <tableColumn id="25" xr3:uid="{F4682446-58E1-4CA5-A48B-3BFAAE53764B}" name="ItemType" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{0088744F-16F9-49C6-BB37-951ECCA67027}" name="CD" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{C97EB513-D794-47F8-B80D-94506BD82E97}" name="Target" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{47C97BCD-31D5-47E8-A5C1-ECCF343A6E95}" name="isCopy" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1678,7 +1783,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
@@ -1690,7 +1795,7 @@
     <col min="10" max="16384" width="16.26953125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -1721,8 +1826,11 @@
       <c r="J1" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="15">
+      <c r="K1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15">
       <c r="A2" s="14" t="s">
         <v>71</v>
       </c>
@@ -1753,8 +1861,11 @@
       <c r="J2" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="15">
+      <c r="K2" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15">
       <c r="A3" s="14" t="s">
         <v>72</v>
       </c>
@@ -1785,8 +1896,11 @@
       <c r="J3" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+      <c r="K3" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15">
       <c r="A4" s="14" t="s">
         <v>73</v>
       </c>
@@ -1817,8 +1931,11 @@
       <c r="J4" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="15">
+      <c r="K4" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15">
       <c r="A5" s="14" t="s">
         <v>74</v>
       </c>
@@ -1848,6 +1965,9 @@
       </c>
       <c r="J5" s="6" t="b">
         <v>0</v>
+      </c>
+      <c r="K5" s="6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1862,7 +1982,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27ECECD7-19E1-4627-A931-18B44035B88A}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="26.54296875" customWidth="1"/>
@@ -1873,7 +1993,7 @@
     <col min="8" max="8" width="9.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1">
+    <row r="1" spans="1:12" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -1907,8 +2027,11 @@
       <c r="K1" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15">
+      <c r="L1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15">
       <c r="A2" s="13" t="s">
         <v>75</v>
       </c>
@@ -1942,8 +2065,11 @@
       <c r="K2" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="15">
+      <c r="L2" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15">
       <c r="A3" s="13" t="s">
         <v>77</v>
       </c>
@@ -1977,8 +2103,11 @@
       <c r="K3" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15">
+      <c r="L3" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" s="13" t="s">
         <v>76</v>
       </c>
@@ -2012,8 +2141,11 @@
       <c r="K4" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="15">
+      <c r="L4" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15">
       <c r="A5" s="13" t="s">
         <v>78</v>
       </c>
@@ -2047,8 +2179,11 @@
       <c r="K5" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="15">
+      <c r="L5" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15">
       <c r="A6" s="13" t="s">
         <v>90</v>
       </c>
@@ -2082,8 +2217,11 @@
       <c r="K6" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="15">
+      <c r="L6" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15">
       <c r="A7" s="13" t="s">
         <v>88</v>
       </c>
@@ -2117,8 +2255,11 @@
       <c r="K7" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="15">
+      <c r="L7" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15">
       <c r="A8" s="13" t="s">
         <v>79</v>
       </c>
@@ -2152,8 +2293,11 @@
       <c r="K8" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="15">
+      <c r="L8" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15">
       <c r="A9" s="13" t="s">
         <v>80</v>
       </c>
@@ -2187,8 +2331,11 @@
       <c r="K9" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="15">
+      <c r="L9" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15">
       <c r="A10" s="13" t="s">
         <v>81</v>
       </c>
@@ -2222,8 +2369,11 @@
       <c r="K10" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="15">
+      <c r="L10" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15">
       <c r="A11" s="13" t="s">
         <v>101</v>
       </c>
@@ -2255,8 +2405,11 @@
       <c r="K11" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="15">
+      <c r="L11" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15">
       <c r="A12" s="13" t="s">
         <v>82</v>
       </c>
@@ -2290,8 +2443,11 @@
       <c r="K12" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="15">
+      <c r="L12" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15">
       <c r="A13" s="13" t="s">
         <v>83</v>
       </c>
@@ -2325,8 +2481,11 @@
       <c r="K13" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="15">
+      <c r="L13" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15">
       <c r="A14" s="13" t="s">
         <v>84</v>
       </c>
@@ -2359,6 +2518,9 @@
       </c>
       <c r="K14" s="6" t="b">
         <v>0</v>
+      </c>
+      <c r="L14" s="6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2373,7 +2535,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2886CEDB-A2BB-4C5C-B7C0-8A8D819EC72C}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2383,7 +2545,7 @@
     <col min="9" max="9" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -2411,8 +2573,11 @@
       <c r="I1" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15">
+      <c r="J1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15">
       <c r="A2" s="13" t="s">
         <v>91</v>
       </c>
@@ -2440,8 +2605,11 @@
       <c r="I2" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15">
+      <c r="J2" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="A3" s="13" t="s">
         <v>92</v>
       </c>
@@ -2469,8 +2637,11 @@
       <c r="I3" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15">
+      <c r="J3" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="13" t="s">
         <v>93</v>
       </c>
@@ -2498,8 +2669,11 @@
       <c r="I4" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="15">
+      <c r="J4" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="13" t="s">
         <v>102</v>
       </c>
@@ -2526,6 +2700,9 @@
       </c>
       <c r="I5" s="6" t="b">
         <v>0</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2540,7 +2717,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC6B873-DDE4-475A-AF60-FACC4E0D297A}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="28.08984375" customWidth="1"/>
@@ -2549,7 +2726,7 @@
     <col min="5" max="5" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -2577,8 +2754,11 @@
       <c r="I1" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15">
+      <c r="J1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15">
       <c r="A2" s="13" t="s">
         <v>94</v>
       </c>
@@ -2606,8 +2786,11 @@
       <c r="I2" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15">
+      <c r="J2" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="A3" s="13" t="s">
         <v>95</v>
       </c>
@@ -2635,8 +2818,11 @@
       <c r="I3" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15">
+      <c r="J3" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="13" t="s">
         <v>96</v>
       </c>
@@ -2664,8 +2850,11 @@
       <c r="I4" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="15">
+      <c r="J4" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="13" t="s">
         <v>97</v>
       </c>
@@ -2692,6 +2881,9 @@
       </c>
       <c r="I5" s="6" t="b">
         <v>0</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2705,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AD825F-9D60-45E2-BB99-D449EDBAE2E8}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.7265625" customWidth="1"/>
@@ -2719,7 +2911,7 @@
     <col min="10" max="10" width="11.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:11" ht="15">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -2750,8 +2942,11 @@
       <c r="J1" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="15">
+      <c r="K1" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15">
       <c r="A2" s="13" t="s">
         <v>100</v>
       </c>
@@ -2782,8 +2977,11 @@
       <c r="J2" s="6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="15">
+      <c r="K2" s="17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15">
       <c r="A3" s="13" t="s">
         <v>98</v>
       </c>
@@ -2814,6 +3012,15 @@
       <c r="J3" s="6" t="b">
         <v>0</v>
       </c>
+      <c r="K3" s="18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="K4" s="17"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="K5" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>

--- a/Src/Assets/Common/Tables/Tables/ActionDefine.xlsx
+++ b/Src/Assets/Common/Tables/Tables/ActionDefine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576589CE-977A-44E0-A702-DA6C231890B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71D987D-8397-4108-9F0D-7BEB0CB52993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="599" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="117">
   <si>
     <t>ID</t>
   </si>
@@ -441,6 +441,42 @@
   </si>
   <si>
     <t>isBasic</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>powder_keg</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>火药桶</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得五颗子弹</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>triple_bullet</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>三补</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得三颗子弹</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>triple_sword</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>三拔</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得三拔剑</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -705,7 +741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -757,6 +793,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="60% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -774,63 +813,6 @@
     <cellStyle name="适中 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
   </cellStyles>
   <dxfs count="40">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -969,6 +951,25 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1018,6 +1019,25 @@
         <patternFill patternType="none"/>
       </fill>
       <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1287,6 +1307,25 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="9"/>
         <color auto="1"/>
         <name val="微软雅黑"/>
@@ -1398,8 +1437,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A1:K5" totalsRowShown="0">
-  <autoFilter ref="A1:K5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A1:K9" totalsRowShown="0">
+  <autoFilter ref="A1:K9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Key" dataDxfId="39"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ID" dataDxfId="38"/>
@@ -1411,7 +1450,7 @@
     <tableColumn id="2" xr3:uid="{B346CB5C-591C-4832-AA88-E75EBEBACD7E}" name="SupplyNumber" dataDxfId="33"/>
     <tableColumn id="7" xr3:uid="{19483CEF-26D9-45EB-902B-73AF0CD7D822}" name="Target" dataDxfId="32"/>
     <tableColumn id="8" xr3:uid="{C1E521C5-2F45-4AF1-A7CA-5C0C319A0BA4}" name="isCopy" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{9FDE5295-D11E-43B2-A44D-C11A54483AC1}" name="isBasic" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{9FDE5295-D11E-43B2-A44D-C11A54483AC1}" name="isBasic" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1421,15 +1460,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}" name="表1_3" displayName="表1_3" ref="A1:L14" totalsRowShown="0">
   <autoFilter ref="A1:L14" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{F3120D7C-A45E-4FA2-B5BE-40DA2E6B527D}" name="Key" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{DACBB893-CA05-4D02-85D5-4BD88763CDC8}" name="ID" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{E05E1824-9A14-47F2-A1F4-06305E7C3F01}" name="Name" dataDxfId="28"/>
-    <tableColumn id="24" xr3:uid="{05C56AEC-8EEB-4DC5-90D4-589693695F9F}" name="Description" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{ECB0F01F-2D12-43FF-88D0-8932B311B9C3}" name="Costs" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{F3120D7C-A45E-4FA2-B5BE-40DA2E6B527D}" name="Key" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{DACBB893-CA05-4D02-85D5-4BD88763CDC8}" name="ID" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{E05E1824-9A14-47F2-A1F4-06305E7C3F01}" name="Name" dataDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{05C56AEC-8EEB-4DC5-90D4-589693695F9F}" name="Description" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{ECB0F01F-2D12-43FF-88D0-8932B311B9C3}" name="Costs" dataDxfId="25"/>
     <tableColumn id="11" xr3:uid="{8738C2BC-B1DC-4B88-A546-C9264D49325B}" name="TargetType"/>
-    <tableColumn id="6" xr3:uid="{A4A2D2D8-BA27-47D8-82A1-4708B0912A01}" name="CD" dataDxfId="25"/>
-    <tableColumn id="27" xr3:uid="{C523F30B-8528-475C-AB56-584489F12893}" name="Level" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{9F4863C8-14DF-490F-AAED-DA9CA6CCA3A6}" name="Damage" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{A4A2D2D8-BA27-47D8-82A1-4708B0912A01}" name="CD" dataDxfId="24"/>
+    <tableColumn id="27" xr3:uid="{C523F30B-8528-475C-AB56-584489F12893}" name="Level" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{9F4863C8-14DF-490F-AAED-DA9CA6CCA3A6}" name="Damage" dataDxfId="22"/>
     <tableColumn id="7" xr3:uid="{BB9F36B2-6C79-4196-AF6D-E44CF2743583}" name="Target"/>
     <tableColumn id="8" xr3:uid="{900D3857-3743-4154-8A5A-A6F00B9A5F63}" name="isCopy"/>
     <tableColumn id="9" xr3:uid="{02DAE644-A845-4C22-A687-D868D5A5B60F}" name="isBasic"/>
@@ -1442,16 +1481,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BBDA416B-0922-4AAF-A799-D524740B3D14}" name="表1_4" displayName="表1_4" ref="A1:J5" totalsRowShown="0">
   <autoFilter ref="A1:J5" xr:uid="{BBDA416B-0922-4AAF-A799-D524740B3D14}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{BE94463F-5F58-4AE5-8D3C-9ED629948C9E}" name="Key" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{65052D3C-90DB-42DF-8C3A-74AA612BEF48}" name="ID" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{2510B181-E22D-4568-AC36-382E43DA1F65}" name="Name" dataDxfId="20"/>
-    <tableColumn id="24" xr3:uid="{4BE18853-2496-4AA4-942D-324B9DDFB7C9}" name="Description" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{002F1A29-9EEC-44DB-A228-41BEF0AE2B11}" name="Costs" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{BE94463F-5F58-4AE5-8D3C-9ED629948C9E}" name="Key" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{65052D3C-90DB-42DF-8C3A-74AA612BEF48}" name="ID" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{2510B181-E22D-4568-AC36-382E43DA1F65}" name="Name" dataDxfId="19"/>
+    <tableColumn id="24" xr3:uid="{4BE18853-2496-4AA4-942D-324B9DDFB7C9}" name="Description" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{002F1A29-9EEC-44DB-A228-41BEF0AE2B11}" name="Costs" dataDxfId="17"/>
     <tableColumn id="11" xr3:uid="{45609FCE-4413-4353-9C89-BD89EFDE4C5D}" name="TargetType"/>
     <tableColumn id="4" xr3:uid="{3D0100FB-1F43-427C-8534-CDC24303D7E6}" name="CD"/>
-    <tableColumn id="6" xr3:uid="{734D322F-5955-4217-B185-B14B145BEC2D}" name="Target" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{D2799729-A837-4530-BC5D-075F4F0C2481}" name="isCopy" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{2A54B557-3CDD-4506-B6E3-5A3D296C44C8}" name="isBasic" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{734D322F-5955-4217-B185-B14B145BEC2D}" name="Target" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{D2799729-A837-4530-BC5D-075F4F0C2481}" name="isCopy" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{2A54B557-3CDD-4506-B6E3-5A3D296C44C8}" name="isBasic" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1461,16 +1500,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8B3284A1-AA19-4A39-984C-72F0ECC55A5D}" name="表1_45" displayName="表1_45" ref="A1:J5" totalsRowShown="0">
   <autoFilter ref="A1:J5" xr:uid="{8B3284A1-AA19-4A39-984C-72F0ECC55A5D}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A1AF415F-7938-4DF8-BACD-2F3931097179}" name="Key" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{0F312E1F-9C3E-4D2C-9F68-C6E87C1EE718}" name="ID" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{B5C76171-0265-42F6-8D5B-4662AAE7F83A}" name="Name" dataDxfId="13"/>
-    <tableColumn id="24" xr3:uid="{25AD89C3-2F76-4593-98BE-A3775460F142}" name="Description" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00DA4CE3-ED05-49B6-9190-58A0333EB78C}" name="Costs" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{A1AF415F-7938-4DF8-BACD-2F3931097179}" name="Key" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{0F312E1F-9C3E-4D2C-9F68-C6E87C1EE718}" name="ID" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{B5C76171-0265-42F6-8D5B-4662AAE7F83A}" name="Name" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{25AD89C3-2F76-4593-98BE-A3775460F142}" name="Description" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00DA4CE3-ED05-49B6-9190-58A0333EB78C}" name="Costs" dataDxfId="9"/>
     <tableColumn id="11" xr3:uid="{E2FEB15A-3782-40F3-A1CA-89D1DDC325AD}" name="TargetType"/>
     <tableColumn id="4" xr3:uid="{688FFF09-C71B-441C-B52A-14B5A669665E}" name="CD"/>
     <tableColumn id="6" xr3:uid="{98986103-0D74-481E-9EA2-26D93ECAF330}" name="Target"/>
     <tableColumn id="7" xr3:uid="{E9536439-71EB-48E6-A500-A711FD55C3A4}" name="isCopy"/>
-    <tableColumn id="8" xr3:uid="{A6F03304-4F13-4C9E-AD7B-C635338D9070}" name="isBasic" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{A6F03304-4F13-4C9E-AD7B-C635338D9070}" name="isBasic" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1480,16 +1519,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CE1C72CE-D78A-4387-BD89-90EB97964EC3}" name="表1_6" displayName="表1_6" ref="A1:J3" totalsRowShown="0">
   <autoFilter ref="A1:J3" xr:uid="{CE1C72CE-D78A-4387-BD89-90EB97964EC3}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{18D4AA6C-FD21-4782-A770-E2A7E552A9B6}" name="Key" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{851BEEEC-EFAC-48C5-98CB-946D8978B5CF}" name="ID" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{9BAC052E-D5DE-43D9-917B-63EC0ABA7487}" name="Name" dataDxfId="8"/>
-    <tableColumn id="24" xr3:uid="{1FC82ABF-F7E7-4151-BE48-531952D84F64}" name="Description" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{18D4AA6C-FD21-4782-A770-E2A7E552A9B6}" name="Key" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{851BEEEC-EFAC-48C5-98CB-946D8978B5CF}" name="ID" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{9BAC052E-D5DE-43D9-917B-63EC0ABA7487}" name="Name" dataDxfId="5"/>
+    <tableColumn id="24" xr3:uid="{1FC82ABF-F7E7-4151-BE48-531952D84F64}" name="Description" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{8B51D4EE-CB38-4B13-AF2A-6B841C4BBE98}" name="Costs"/>
     <tableColumn id="11" xr3:uid="{5A33598E-528B-42B6-9450-35112F1912EB}" name="TargetType"/>
-    <tableColumn id="25" xr3:uid="{F4682446-58E1-4CA5-A48B-3BFAAE53764B}" name="ItemType" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{0088744F-16F9-49C6-BB37-951ECCA67027}" name="CD" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{C97EB513-D794-47F8-B80D-94506BD82E97}" name="Target" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{47C97BCD-31D5-47E8-A5C1-ECCF343A6E95}" name="isCopy" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{F4682446-58E1-4CA5-A48B-3BFAAE53764B}" name="ItemType" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{0088744F-16F9-49C6-BB37-951ECCA67027}" name="CD" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C97EB513-D794-47F8-B80D-94506BD82E97}" name="Target" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{47C97BCD-31D5-47E8-A5C1-ECCF343A6E95}" name="isCopy" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1783,7 +1822,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
@@ -1969,6 +2008,122 @@
       <c r="K5" s="6" t="b">
         <v>1</v>
       </c>
+    </row>
+    <row r="6" spans="1:11" ht="15">
+      <c r="A6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15">
+      <c r="A7" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15">
+      <c r="A8" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="19"/>
+      <c r="G9"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>

--- a/Src/Assets/Common/Tables/Tables/ActionDefine.xlsx
+++ b/Src/Assets/Common/Tables/Tables/ActionDefine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
-  <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CCA456\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71D987D-8397-4108-9F0D-7BEB0CB52993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC965A9D-2A3A-4692-AEF8-B7E2599C2105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply" sheetId="1" r:id="rId1"/>
@@ -20,16 +20,11 @@
     <sheet name="Special" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="120">
   <si>
     <t>ID</t>
   </si>
@@ -479,6 +474,17 @@
     <t>获得三拔剑</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
+  <si>
+    <t>EXcalibur</t>
+  </si>
+  <si>
+    <t>大宝剑</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excalibur</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -487,7 +493,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -628,8 +634,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -670,6 +690,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.992828150273141E-2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -741,7 +767,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -756,9 +782,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -777,7 +800,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -794,6 +817,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1457,8 +1498,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}" name="表1_3" displayName="表1_3" ref="A1:L14" totalsRowShown="0">
-  <autoFilter ref="A1:L14" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}" name="表1_3" displayName="表1_3" ref="A1:L16" totalsRowShown="0">
+  <autoFilter ref="A1:L16" xr:uid="{6AAE696F-C7CE-4533-8F63-E9BDB46E5712}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{F3120D7C-A45E-4FA2-B5BE-40DA2E6B527D}" name="Key" dataDxfId="29"/>
     <tableColumn id="3" xr3:uid="{DACBB893-CA05-4D02-85D5-4BD88763CDC8}" name="ID" dataDxfId="28"/>
@@ -1823,15 +1864,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="16.21875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.90625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.36328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16.26953125" style="2"/>
-    <col min="10" max="16384" width="16.26953125" style="2"/>
+    <col min="2" max="2" width="22.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.21875" style="2"/>
+    <col min="10" max="16384" width="16.21875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1853,16 +1894,16 @@
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>49</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>105</v>
       </c>
       <c r="K1" s="2" t="s">
@@ -1870,10 +1911,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -1885,7 +1926,7 @@
       <c r="E2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G2">
@@ -1894,21 +1935,21 @@
       <c r="H2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6" t="b">
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1920,7 +1961,7 @@
       <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G3">
@@ -1929,21 +1970,21 @@
       <c r="H3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6" t="b">
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1955,7 +1996,7 @@
       <c r="E4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G4">
@@ -1964,21 +2005,21 @@
       <c r="H4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6" t="b">
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1990,7 +2031,7 @@
       <c r="E5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G5">
@@ -1999,21 +2040,21 @@
       <c r="H5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6" t="b">
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2025,7 +2066,7 @@
       <c r="E6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G6">
@@ -2034,21 +2075,21 @@
       <c r="H6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6" t="b">
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>111</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2060,7 +2101,7 @@
       <c r="E7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G7">
@@ -2069,21 +2110,21 @@
       <c r="H7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6" t="b">
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>114</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2095,7 +2136,7 @@
       <c r="E8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G8">
@@ -2104,26 +2145,23 @@
       <c r="H8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6" t="b">
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="19"/>
+      <c r="F9" s="18"/>
       <c r="G9"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -2137,15 +2175,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27ECECD7-19E1-4627-A931-18B44035B88A}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="26.54296875" customWidth="1"/>
-    <col min="2" max="2" width="26.7265625" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" customWidth="1"/>
-    <col min="4" max="4" width="46.6328125" customWidth="1"/>
-    <col min="5" max="5" width="18.26953125" customWidth="1"/>
-    <col min="8" max="8" width="9.54296875" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1">
@@ -2167,7 +2205,7 @@
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>49</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -2176,10 +2214,10 @@
       <c r="I1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>105</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -2187,10 +2225,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="15">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2202,7 +2240,7 @@
       <c r="E2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G2">
@@ -2211,24 +2249,24 @@
       <c r="H2" s="5">
         <v>2</v>
       </c>
-      <c r="I2" s="6">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6" t="b">
+      <c r="I2" s="5">
+        <v>1</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>77</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2240,33 +2278,33 @@
       <c r="E3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>3</v>
       </c>
-      <c r="I3" s="6">
-        <v>1</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6" t="b">
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2278,33 +2316,33 @@
       <c r="E4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>2</v>
       </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6" t="b">
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>78</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2316,33 +2354,33 @@
       <c r="E5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>2</v>
       </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6" t="b">
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2354,33 +2392,33 @@
       <c r="E6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>5</v>
       </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6" t="b">
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2392,291 +2430,339 @@
       <c r="E7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>5</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6" t="b">
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <v>7</v>
+      </c>
+      <c r="I8" s="24">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15">
+      <c r="A9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>4</v>
       </c>
-      <c r="I8" s="6">
-        <v>1</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15">
-      <c r="A9" s="13" t="s">
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15">
+      <c r="A10" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D10" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>4</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15">
-      <c r="A10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="12">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
         <v>4</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15">
+      <c r="A11" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4</v>
+      </c>
+      <c r="I11" s="5">
         <v>2</v>
       </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15">
-      <c r="A11" s="13" t="s">
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15">
+      <c r="A12" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15">
-      <c r="A12" s="13" t="s">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15">
+      <c r="A13" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
         <v>6</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I13" s="5">
         <v>2</v>
       </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15">
-      <c r="A13" s="13" t="s">
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15">
+      <c r="A14" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
         <v>6</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I14" s="5">
         <v>3</v>
       </c>
-      <c r="J13" s="6">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15">
-      <c r="A14" s="13" t="s">
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15">
+      <c r="A15" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
         <v>7</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I15" s="5">
         <v>3</v>
       </c>
-      <c r="J14" s="6">
-        <v>0</v>
-      </c>
-      <c r="K14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6" t="b">
-        <v>1</v>
-      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -2691,13 +2777,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2886CEDB-A2BB-4C5C-B7C0-8A8D819EC72C}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="17.7265625" customWidth="1"/>
-    <col min="4" max="4" width="48.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.08984375" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
+    <col min="4" max="4" width="48.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2719,13 +2805,13 @@
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>105</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -2733,10 +2819,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2745,30 +2831,30 @@
       <c r="D2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="b">
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>92</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2777,30 +2863,30 @@
       <c r="D3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="b">
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2809,30 +2895,30 @@
       <c r="D4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="b">
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2841,22 +2927,22 @@
       <c r="D5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="b">
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2873,12 +2959,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC6B873-DDE4-475A-AF60-FACC4E0D297A}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="4" max="4" width="71.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="4" max="4" width="71.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2900,13 +2986,13 @@
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>105</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -2914,42 +3000,42 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="b">
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>95</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2958,30 +3044,30 @@
       <c r="D3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="b">
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2990,30 +3076,30 @@
       <c r="D4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="b">
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3022,22 +3108,22 @@
       <c r="D5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="b">
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3053,17 +3139,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AD825F-9D60-45E2-BB99-D449EDBAE2E8}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" customWidth="1"/>
     <col min="4" max="4" width="78" customWidth="1"/>
-    <col min="5" max="5" width="19.6328125" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" customWidth="1"/>
-    <col min="10" max="10" width="11.36328125" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15">
@@ -3079,7 +3165,7 @@
       <c r="D1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -3088,24 +3174,24 @@
       <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3117,30 +3203,30 @@
       <c r="E2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="17" t="b">
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3152,30 +3238,30 @@
       <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="6">
-        <v>1</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="18" t="b">
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="17" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="K4" s="17"/>
+      <c r="K4" s="16"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="K5" s="18"/>
+      <c r="K5" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
